--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1049,6 +1049,462 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114733554</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97528</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 941, Hjulby, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587843</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6425963</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114733507</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97528</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 941, Hjulby, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>587824</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6425971</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114733522</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97528</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 941, Hjulby, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>587908</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6425925</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114733495</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97528</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 941, Hjulby, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>587802</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6425969</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74969345</v>
       </c>
       <c r="B2" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587968.5942186569</v>
+        <v>587969</v>
       </c>
       <c r="R2" t="n">
-        <v>6425975.581435055</v>
+        <v>6425976</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74969345</v>
       </c>
       <c r="B2" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74969345</v>
       </c>
       <c r="B2" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74969345</v>
       </c>
       <c r="B2" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74969345</v>
       </c>
       <c r="B2" t="n">
-        <v>109477</v>
+        <v>109483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74969345</v>
       </c>
       <c r="B2" t="n">
-        <v>109483</v>
+        <v>109490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74969345</v>
       </c>
       <c r="B2" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74969345</v>
       </c>
       <c r="B2" t="n">
-        <v>109494</v>
+        <v>109502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74969345</v>
       </c>
       <c r="B2" t="n">
-        <v>109505</v>
+        <v>109510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74969345</v>
       </c>
       <c r="B2" t="n">
-        <v>109510</v>
+        <v>109518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74969345</v>
       </c>
       <c r="B2" t="n">
-        <v>109518</v>
+        <v>109528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 941-2024 artfynd.xlsx
+++ b/artfynd/A 941-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>74969345</v>
       </c>
       <c r="B2" t="n">
-        <v>109528</v>
+        <v>110077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,12 +789,7 @@
         <v>98299418</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587803.4682469</v>
+        <v>587803</v>
       </c>
       <c r="R3" t="n">
-        <v>6425965.583360081</v>
+        <v>6425966</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +866,9 @@
           <t>2022-01-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-01-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,12 +899,7 @@
         <v>98299595</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587826.9431636593</v>
+        <v>587827</v>
       </c>
       <c r="R4" t="n">
-        <v>6425961.853810706</v>
+        <v>6425962</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,19 +976,9 @@
           <t>2022-01-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-01-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,15 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114733554</v>
+        <v>98299764</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,7 +1034,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1080,14 +1049,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 941, Hjulby, Sm</t>
+          <t>A 1677, Sandebo, Lofta, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587843</v>
+        <v>587792</v>
       </c>
       <c r="R5" t="n">
-        <v>6425963</v>
+        <v>6425956</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,12 +1083,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2022-01-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2022-01-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,12 +1119,7 @@
         <v>114733495</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,15 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114733522</v>
+        <v>114733507</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1256,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1314,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587908</v>
+        <v>587824</v>
       </c>
       <c r="R7" t="n">
-        <v>6425925</v>
+        <v>6425971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,15 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114733507</v>
+        <v>114733522</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1366,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1429,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587824</v>
+        <v>587908</v>
       </c>
       <c r="R8" t="n">
-        <v>6425971</v>
+        <v>6425925</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1489,6 +1443,112 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114733554</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 941, Hjulby, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>587843</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6425963</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
